--- a/SGC-CKN/Excel/c42522c4-3bb6-4fc0-a1eb-5a9618f2b505_Cọc_khoan_nhồi_P1-49_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/c42522c4-3bb6-4fc0-a1eb-5a9618f2b505_Cọc_khoan_nhồi_P1-49_D800_31-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,11 +98,11 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t xml:space="preserve">15:50
+    <t xml:space="preserve">15:30
 30/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:22
+    <t xml:space="preserve">15:32
 30/03/2026</t>
   </si>
   <si>
@@ -115,11 +115,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">16:23
+    <t xml:space="preserve">15:33
 30/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:45
+    <t xml:space="preserve">15:45
 30/03/2026</t>
   </si>
   <si>
@@ -129,11 +129,11 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">16:46
+    <t xml:space="preserve">15:46
 30/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:56
+    <t xml:space="preserve">15:56
 30/03/2026</t>
   </si>
   <si>
@@ -143,7 +143,7 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">16:57
+    <t xml:space="preserve">15:57
 30/03/2026</t>
   </si>
   <si>
@@ -185,10 +185,6 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">19:45
-30/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">22:35
 30/03/2026</t>
   </si>
@@ -200,7 +196,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:15
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>Kết thúc khoan</t>
@@ -352,17 +348,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -378,6 +369,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -523,35 +519,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1175,16 +1171,16 @@
         <v>-0.76</v>
       </c>
       <c r="G11" s="5">
-        <v>-2.78</v>
+        <v>-0.95</v>
       </c>
       <c r="H11" s="5">
-        <v>0.53</v>
+        <v>0.03</v>
       </c>
       <c r="I11" s="5">
-        <v>2.02</v>
+        <v>0.19</v>
       </c>
       <c r="J11" s="8">
-        <v>3.79</v>
+        <v>5.7</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1207,126 +1203,126 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-2.78</v>
+        <v>-0.95</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.05</v>
+        <v>-4.05</v>
       </c>
       <c r="H12" s="9">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="9">
-        <v>6.27</v>
-      </c>
-      <c r="J12" s="12">
-        <v>17.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>15.5</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="13">
-        <v>-9.05</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="F13" s="12">
+        <v>-4.05</v>
+      </c>
+      <c r="G13" s="12">
+        <v>-7.35</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.17</v>
+      </c>
+      <c r="I13" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="J13" s="8">
+        <v>19.8</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="15">
+        <v>-7.35</v>
+      </c>
+      <c r="G14" s="15">
         <v>-16.15</v>
       </c>
-      <c r="H13" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="I13" s="13">
-        <v>7.1</v>
-      </c>
-      <c r="J13" s="12">
-        <v>42.6</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="H14" s="15">
+        <v>1.47</v>
+      </c>
+      <c r="I14" s="15">
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="8">
+        <v>6</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="16" t="s">
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="16">
+      <c r="C15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="18">
         <v>-16.15</v>
       </c>
-      <c r="G14" s="16">
-        <v>-26.5</v>
-      </c>
-      <c r="H14" s="16">
-        <v>0.47</v>
-      </c>
-      <c r="I14" s="16">
-        <v>10.35</v>
-      </c>
-      <c r="J14" s="12">
-        <v>22.18</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="19">
-        <v>-26.5</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-30</v>
-      </c>
-      <c r="H15" s="19">
+      <c r="G15" s="18">
+        <v>-21.3</v>
+      </c>
+      <c r="H15" s="18">
         <v>1.18</v>
       </c>
-      <c r="I15" s="19">
-        <v>3.5</v>
-      </c>
-      <c r="J15" s="8">
-        <v>2.96</v>
-      </c>
-      <c r="K15" s="20" t="s">
+      <c r="I15" s="18">
+        <v>5.15</v>
+      </c>
+      <c r="J15" s="21">
+        <v>4.35</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1347,19 +1343,19 @@
         <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>-30</v>
+        <v>-21.3</v>
       </c>
       <c r="G16" s="22">
-        <v>-39.3</v>
+        <v>-25.35</v>
       </c>
       <c r="H16" s="22">
         <v>0.62</v>
       </c>
       <c r="I16" s="22">
-        <v>9.3</v>
-      </c>
-      <c r="J16" s="12">
-        <v>15.08</v>
+        <v>4.05</v>
+      </c>
+      <c r="J16" s="8">
+        <v>6.57</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1376,25 +1372,25 @@
         <v>52</v>
       </c>
       <c r="D17" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>54</v>
-      </c>
       <c r="F17" s="25">
+        <v>-25.35</v>
+      </c>
+      <c r="G17" s="25">
         <v>-39.3</v>
       </c>
-      <c r="G17" s="25">
-        <v>-44.26</v>
-      </c>
       <c r="H17" s="25">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="I17" s="25">
-        <v>4.96</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1.75</v>
+        <v>13.95</v>
+      </c>
+      <c r="J17" s="21">
+        <v>4.18</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1402,22 +1398,22 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>57</v>
-      </c>
       <c r="F18" s="28">
-        <v>-44.26</v>
+        <v>-39.3</v>
       </c>
       <c r="G18" s="28">
         <v>-44.26</v>
@@ -1426,18 +1422,18 @@
         <v>1.67</v>
       </c>
       <c r="I18" s="28">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8">
-        <v>0</v>
+        <v>4.96</v>
+      </c>
+      <c r="J18" s="21">
+        <v>2.98</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1543,31 +1539,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1587,16 +1583,16 @@
         <v>-0.76</v>
       </c>
       <c r="F2" s="5">
-        <v>-2.78</v>
+        <v>-0.95</v>
       </c>
       <c r="G2" s="5">
-        <v>0.53</v>
+        <v>0.03</v>
       </c>
       <c r="H2" s="5">
-        <v>2.02</v>
+        <v>0.19</v>
       </c>
       <c r="I2" s="8">
-        <v>3.79</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1613,106 +1609,106 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-2.78</v>
+        <v>-0.95</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.05</v>
+        <v>-4.05</v>
       </c>
       <c r="G3" s="9">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="9">
-        <v>6.27</v>
-      </c>
-      <c r="I3" s="12">
-        <v>17.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>15.5</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-9.05</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
+        <v>-4.05</v>
+      </c>
+      <c r="F4" s="12">
+        <v>-7.35</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.17</v>
+      </c>
+      <c r="H4" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="I4" s="8">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
+        <v>-7.35</v>
+      </c>
+      <c r="F5" s="15">
         <v>-16.15</v>
       </c>
-      <c r="G4" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="H4" s="13">
-        <v>7.1</v>
-      </c>
-      <c r="I4" s="12">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="G5" s="15">
+        <v>1.47</v>
+      </c>
+      <c r="H5" s="15">
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E6" s="18">
         <v>-16.15</v>
       </c>
-      <c r="F5" s="16">
-        <v>-26.5</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.47</v>
-      </c>
-      <c r="H5" s="16">
-        <v>10.35</v>
-      </c>
-      <c r="I5" s="12">
-        <v>22.18</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="19">
-        <v>1</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-26.5</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-30</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="F6" s="18">
+        <v>-21.3</v>
+      </c>
+      <c r="G6" s="18">
         <v>1.18</v>
       </c>
-      <c r="H6" s="19">
-        <v>3.5</v>
-      </c>
-      <c r="I6" s="8">
-        <v>2.96</v>
+      <c r="H6" s="18">
+        <v>5.15</v>
+      </c>
+      <c r="I6" s="21">
+        <v>4.35</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1729,19 +1725,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-30</v>
+        <v>-21.3</v>
       </c>
       <c r="F7" s="22">
-        <v>-39.3</v>
+        <v>-25.35</v>
       </c>
       <c r="G7" s="22">
         <v>0.62</v>
       </c>
       <c r="H7" s="22">
-        <v>9.3</v>
-      </c>
-      <c r="I7" s="12">
-        <v>15.08</v>
+        <v>4.05</v>
+      </c>
+      <c r="I7" s="8">
+        <v>6.57</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1758,19 +1754,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
+        <v>-25.35</v>
+      </c>
+      <c r="F8" s="25">
         <v>-39.3</v>
       </c>
-      <c r="F8" s="25">
-        <v>-44.26</v>
-      </c>
       <c r="G8" s="25">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="H8" s="25">
-        <v>4.96</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1.75</v>
+        <v>13.95</v>
+      </c>
+      <c r="I8" s="21">
+        <v>4.18</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1781,13 +1777,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-44.26</v>
+        <v>-39.3</v>
       </c>
       <c r="F9" s="28">
         <v>-44.26</v>
@@ -1796,15 +1792,15 @@
         <v>1.67</v>
       </c>
       <c r="H9" s="28">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
+        <v>4.96</v>
+      </c>
+      <c r="I9" s="21">
+        <v>2.98</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1822,13 +1818,13 @@
         <v>-44.26</v>
       </c>
       <c r="G10" s="33">
-        <v>7.83</v>
+        <v>8.67</v>
       </c>
       <c r="H10" s="33">
         <v>43.5</v>
       </c>
       <c r="I10" s="33">
-        <v>5.55</v>
+        <v>5.02</v>
       </c>
     </row>
   </sheetData>
